--- a/Data/CombinedInputs-V1-Baseline.xlsx
+++ b/Data/CombinedInputs-V1-Baseline.xlsx
@@ -705,7 +705,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3689,7 +3689,7 @@
     <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.25">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
@@ -4098,7 +4098,7 @@
     <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
@@ -5236,7 +5236,7 @@
     <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="24" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
@@ -6325,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="3">
-        <v>0</v>
+        <v>0.57142857142857162</v>
       </c>
       <c r="E2" s="3">
         <v>0</v>
@@ -6388,8 +6388,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.57142857142857162</v>
       </c>
       <c r="G3" s="3">
         <f t="shared" si="1"/>
@@ -6432,7 +6431,7 @@
         <v>70</v>
       </c>
       <c r="B4" s="3">
-        <f t="shared" ref="B3:B9" si="3">1/7</f>
+        <f t="shared" ref="B4:B9" si="3">1/7</f>
         <v>0.14285714285714285</v>
       </c>
       <c r="C4" s="3">
@@ -6442,15 +6441,14 @@
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3">
         <f t="shared" si="0"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="G4" s="3">
-        <f t="shared" si="1"/>
-        <v>0.14285714285714285</v>
+        <v>0.57142857142857162</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -6489,8 +6487,7 @@
         <v>71</v>
       </c>
       <c r="B5" s="3">
-        <f t="shared" si="3"/>
-        <v>0.14285714285714285</v>
+        <v>0.57142857142857162</v>
       </c>
       <c r="C5" s="3">
         <v>0</v>
@@ -6553,8 +6550,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3">
-        <f t="shared" ref="D5:D9" si="4">1/7</f>
-        <v>0.14285714285714285</v>
+        <v>0.57142857142857162</v>
       </c>
       <c r="E6" s="3">
         <v>0</v>
@@ -6610,21 +6606,20 @@
         <v>0</v>
       </c>
       <c r="D7" s="3">
-        <f t="shared" si="4"/>
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" ref="F7:F9" si="4">1/7</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <f t="shared" ref="F7:F9" si="5">1/7</f>
-        <v>0.14285714285714285</v>
-      </c>
       <c r="G7" s="3">
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I7" s="3">
         <f t="shared" si="2"/>
@@ -6660,21 +6655,20 @@
         <v>74</v>
       </c>
       <c r="B8" s="3">
-        <f t="shared" si="3"/>
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <f t="shared" ref="D6:D9" si="5">1/7</f>
         <v>0.14285714285714285</v>
       </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <f t="shared" si="4"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <f t="shared" si="5"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="G8" s="3">
@@ -6717,25 +6711,24 @@
         <v>75</v>
       </c>
       <c r="B9" s="3">
-        <f t="shared" si="3"/>
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="5"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <f t="shared" si="4"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" si="5"/>
-        <v>0.14285714285714285</v>
-      </c>
       <c r="G9" s="3">
-        <f t="shared" ref="G8:G9" si="6">1/7</f>
+        <f t="shared" ref="G9" si="6">1/7</f>
         <v>0.14285714285714285</v>
       </c>
       <c r="H9" s="3">
@@ -6800,6 +6793,30 @@
       <c r="J10" s="3">
         <v>0</v>
       </c>
+      <c r="K10" s="3">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" ref="N10:O14" si="7">1/7</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O10" s="3">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <f>1/7</f>
+        <v>0.14285714285714285</v>
+      </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -6829,8 +6846,32 @@
       <c r="I11" s="3">
         <v>0</v>
       </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
       <c r="K11" s="3">
         <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <f>1/7</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="O11" s="3">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3">
+        <f t="shared" ref="Q11:Q16" si="8">1/7</f>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -6861,8 +6902,32 @@
       <c r="I12" s="3">
         <v>0</v>
       </c>
+      <c r="J12" s="3">
+        <f t="shared" ref="J12:J17" si="9">1/7</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
       <c r="L12" s="3">
         <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O12" s="3">
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
+        <f t="shared" si="8"/>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -6893,8 +6958,32 @@
       <c r="I13" s="3">
         <v>0</v>
       </c>
+      <c r="J13" s="3">
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
       <c r="M13" s="3">
         <v>1</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O13" s="3">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <f t="shared" si="8"/>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
@@ -6925,8 +7014,32 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
+      <c r="J14" s="3">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
       <c r="N14" s="3">
         <v>1</v>
+      </c>
+      <c r="O14" s="3">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <f t="shared" si="8"/>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
@@ -6957,8 +7070,32 @@
       <c r="I15" s="3">
         <v>0</v>
       </c>
+      <c r="J15" s="3">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <f t="shared" ref="N15:O17" si="10">1/7</f>
+        <v>0.14285714285714285</v>
+      </c>
       <c r="O15" s="3">
         <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="3">
+        <f t="shared" si="8"/>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -6989,8 +7126,32 @@
       <c r="I16" s="3">
         <v>0</v>
       </c>
+      <c r="J16" s="3">
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" ref="L16:L17" si="11">1/7</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="10"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O16" s="3">
+        <v>0</v>
+      </c>
       <c r="P16" s="3">
         <v>1</v>
+      </c>
+      <c r="Q16" s="3">
+        <f t="shared" si="8"/>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
@@ -7019,6 +7180,30 @@
         <v>0</v>
       </c>
       <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.57142857142857162</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <f t="shared" si="11"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
+        <f t="shared" si="10"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O17" s="3">
+        <f t="shared" si="10"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="P17" s="3">
         <v>0</v>
       </c>
       <c r="Q17" s="3">
